--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42953-2024 artfynd.xlsx
+++ b/artfynd/A 42953-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136776463</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136776462</v>
       </c>
       <c r="B3" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
